--- a/team-throughput/customer-ops-1-metric-tracker.xlsx
+++ b/team-throughput/customer-ops-1-metric-tracker.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,9 +30,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <color rgb="FF0A1820"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B828C"/>
     </font>
     <font>
       <b val="1"/>
@@ -43,11 +49,8 @@
       <color rgb="FF0A1820"/>
       <sz val="13"/>
     </font>
-    <font>
-      <color rgb="FF0A1820"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,11 +64,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEEF2F5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -87,36 +95,69 @@
         <color rgb="FFD6DDE1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD6DDE1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD6DDE1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD6DDE1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD6DDE1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -484,219 +525,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12.5" customWidth="1" min="2" max="2"/>
-    <col width="12.5" customWidth="1" min="3" max="3"/>
-    <col width="12.5" customWidth="1" min="4" max="4"/>
-    <col width="12.5" customWidth="1" min="5" max="5"/>
-    <col width="12.5" customWidth="1" min="6" max="6"/>
-    <col width="12.5" customWidth="1" min="7" max="7"/>
-    <col width="12.5" customWidth="1" min="8" max="8"/>
-    <col width="12.5" customWidth="1" min="9" max="9"/>
-    <col width="12.5" customWidth="1" min="10" max="10"/>
-    <col width="12.5" customWidth="1" min="11" max="11"/>
-    <col width="12.5" customWidth="1" min="12" max="12"/>
-    <col width="12.5" customWidth="1" min="13" max="13"/>
-    <col width="12.5" customWidth="1" min="14" max="14"/>
-    <col width="12.5" customWidth="1" min="15" max="15"/>
-    <col width="12.5" customWidth="1" min="16" max="16"/>
-    <col width="12.5" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Week ending</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>REP</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+          <t>Metric  \  Week ending</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n">
+        <v>46171</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Open CUS</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="B2" s="4" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Open REP</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="B3" s="4" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Open total</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>% done</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>% w/ in-prog</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>% done</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>% w/ in-review</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>% done</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="D3" s="6">
-        <f>B3+C3</f>
-        <v/>
-      </c>
-      <c r="E3" s="6" t="n">
+      <c r="B4" s="6">
+        <f>B2+B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>CUS · Created</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CUS · Done</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="7">
-        <f>IF(E3=0,"",F3/E3)</f>
-        <v/>
-      </c>
-      <c r="H3" s="6" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CUS · % done</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>IF(B5=0,"",B6/B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>CUS · In progress (Pending dev)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="7">
-        <f>IF(E3=0,"",(F3+H3)/E3)</f>
-        <v/>
-      </c>
-      <c r="J3" s="6" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CUS · % w/ in-prog</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>IF(B5=0,"",(B6+B8)/B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>REP · Created</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K3" s="6" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>REP · Done</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="7">
-        <f>IF(J3=0,"",K3/J3)</f>
-        <v/>
-      </c>
-      <c r="M3" s="6" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>REP · % done</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <f>IF(B10=0,"",B11/B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>REP · In review</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="N3" s="7">
-        <f>IF(J3=0,"",(K3+M3)/J3)</f>
-        <v/>
-      </c>
-      <c r="O3" s="6">
-        <f>E3+J3</f>
-        <v/>
-      </c>
-      <c r="P3" s="6">
-        <f>F3+K3</f>
-        <v/>
-      </c>
-      <c r="Q3" s="7">
-        <f>IF(O3=0,"",P3/O3)</f>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>REP · % w/ in-review</t>
+        </is>
+      </c>
+      <c r="B14" s="7">
+        <f>IF(B10=0,"",(B11+B13)/B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Total · Created</t>
+        </is>
+      </c>
+      <c r="B15" s="9">
+        <f>B5+B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Total · Done</t>
+        </is>
+      </c>
+      <c r="B16" s="11">
+        <f>B6+B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Total · % done</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>IF(B15=0,"",B16/B15)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -707,219 +729,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12.5" customWidth="1" min="2" max="2"/>
-    <col width="12.5" customWidth="1" min="3" max="3"/>
-    <col width="12.5" customWidth="1" min="4" max="4"/>
-    <col width="12.5" customWidth="1" min="5" max="5"/>
-    <col width="12.5" customWidth="1" min="6" max="6"/>
-    <col width="12.5" customWidth="1" min="7" max="7"/>
-    <col width="12.5" customWidth="1" min="8" max="8"/>
-    <col width="12.5" customWidth="1" min="9" max="9"/>
-    <col width="12.5" customWidth="1" min="10" max="10"/>
-    <col width="12.5" customWidth="1" min="11" max="11"/>
-    <col width="12.5" customWidth="1" min="12" max="12"/>
-    <col width="12.5" customWidth="1" min="13" max="13"/>
-    <col width="12.5" customWidth="1" min="14" max="14"/>
-    <col width="12.5" customWidth="1" min="15" max="15"/>
-    <col width="12.5" customWidth="1" min="16" max="16"/>
-    <col width="12.5" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Week ending</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>CUS</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>REP</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+          <t>Metric  \  Week ending</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n">
+        <v>46171</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Open CUS</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="B2" s="4" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Open REP</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="B3" s="4" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Open total</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>% done</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>% w/ in-prog</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>% done</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>% w/ in-review</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>% done</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="D3" s="6">
-        <f>B3+C3</f>
-        <v/>
-      </c>
-      <c r="E3" s="6" t="n">
+      <c r="B4" s="6">
+        <f>B2+B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>CUS · Created</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="F3" s="6" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CUS · Done</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="7">
-        <f>IF(E3=0,"",F3/E3)</f>
-        <v/>
-      </c>
-      <c r="H3" s="6" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CUS · % done</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>IF(B5=0,"",B6/B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>CUS · In progress (Pending dev)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="7">
-        <f>IF(E3=0,"",(F3+H3)/E3)</f>
-        <v/>
-      </c>
-      <c r="J3" s="6" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CUS · % w/ in-prog</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>IF(B5=0,"",(B6+B8)/B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>REP · Created</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="K3" s="6" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>REP · Done</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="7">
-        <f>IF(J3=0,"",K3/J3)</f>
-        <v/>
-      </c>
-      <c r="M3" s="6" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>REP · % done</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <f>IF(B10=0,"",B11/B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>REP · In review</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="N3" s="7">
-        <f>IF(J3=0,"",(K3+M3)/J3)</f>
-        <v/>
-      </c>
-      <c r="O3" s="6">
-        <f>E3+J3</f>
-        <v/>
-      </c>
-      <c r="P3" s="6">
-        <f>F3+K3</f>
-        <v/>
-      </c>
-      <c r="Q3" s="7">
-        <f>IF(O3=0,"",P3/O3)</f>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>REP · % w/ in-review</t>
+        </is>
+      </c>
+      <c r="B14" s="7">
+        <f>IF(B10=0,"",(B11+B13)/B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Total · Created</t>
+        </is>
+      </c>
+      <c r="B15" s="9">
+        <f>B5+B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Total · Done</t>
+        </is>
+      </c>
+      <c r="B16" s="11">
+        <f>B6+B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Total · % done</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>IF(B15=0,"",B16/B15)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -930,218 +933,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Customer Ops 1 Metric — Tracker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr"/>
+      <c r="A2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Team = Amy, Marco, Latefa, Christophe. Teams covered: CUS (Customer Success) + REP (Reporting).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Counts are pulled from Linear (filter: issue created by one of the four team members).</t>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Counts pulled from Linear (filter: issue created by one of the four team members).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr"/>
+      <c r="A5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>HOW TO USE</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Each row on the 1-Week / 2-Week sheets is one weekly snapshot. To log a new week, add a row, enter the</t>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Layout is transposed: metrics run down column A, and each WEEK is its own column across the top.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>raw counts (white cells), and copy the formula columns (% done, % w/ in-prog, totals) down. Once you have</t>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>To log a new week: copy the latest week's column and paste it into the next empty column to the right,</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>several rows, select a % column + Week ending and Insert &gt; Chart (line) to see the trend.</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>then overwrite the white input cells with the new counts. The grey % / total rows are formulas and</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr"/>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>recalculate automatically. Once you have several week-columns, select a metric row across the weeks</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>COLUMN DEFINITIONS</t>
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>and Insert &gt; Chart (line) to see the trend left-to-right.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>ROW DEFINITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Open CUS / Open REP = tickets currently NOT Done, Canceled, or Duplicate (Triage, Backlog, Todo,</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   In Progress, In Review, etc.), created by the team. Point-in-time snapshot as of the week-ending date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Created = issues the team opened during the window (this week, or trailing 2 weeks).</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Done = of those created in the window, how many are now status Done. (Same-window cohort: a ticket only</t>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   In Progress, In Review, etc.), created by the team. Point-in-time as of the week-ending date.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   counts if it was created AND completed inside the window, so % done can never exceed 100%.)</t>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Created = issues the team opened during the window (1-Week sheet = that week; 2-Week sheet = trailing 2 wks).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Done = of those created in the window, how many are now status Done (same-window cohort; % can't exceed 100%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>% done = Done / Created.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>In progress (CUS) = created-in-window tickets sitting in 'Pending development' (CUS has no In Progress</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   status; Pending dev is its active/handed-to-eng stage).</t>
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>In progress (CUS) = created-in-window tickets in 'Pending development' (CUS has no In Progress status).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>In review (REP) = created-in-window tickets sitting in 'In Review'.</t>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>In review (REP) = created-in-window tickets in 'In Review'.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>% w/ in-prog / % w/ in-review = CUMULATIVE: (Done + in-flight) / Created. Done plus near-finished work —</t>
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>% w/ in-prog / % w/ in-review = CUMULATIVE (Done + in-flight) / Created — a leading indicator.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   a leading indicator of completions about to land.</t>
-        </is>
-      </c>
+      <c r="A22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr"/>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>NOTES</t>
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Backlog-flush days don't inflate this metric (those tickets were opened in earlier windows).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Backlog-flush days (a batch of old tickets closed at once) do NOT inflate this metric, because those</t>
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>1-Week reads low by design (recent tickets haven't had time to close); 2-Week is more meaningful.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   tickets were opened in earlier windows and fail the same-window test.</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Daniela bundle: REP in-review includes REP-315 (umbrella) + sub-reports REP-317/318/319 = 4 tickets, 1 request.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>The 1-Week view reads low by design — tickets opened in the last day or two haven't had time to close.</t>
-        </is>
-      </c>
+      <c r="A27" s="14" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   The 2-Week view is the more meaningful one.</t>
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Snapshot pre-filled for week ending 2026-05-29. Companion dashboard:</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Daniela bundle: REP in-review includes REP-315 (umbrella) + its 3 sub-reports REP-317/318/319 —</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   counted as 4 tickets but representing one bundled request.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Snapshot pre-filled for week ending 2026-05-29. Companion dashboard:</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>https://amytread.github.io/customer-ops-hub/team-throughput/</t>
         </is>
